--- a/Resultados de adivina el número.xlsx
+++ b/Resultados de adivina el número.xlsx
@@ -1,121 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miguelangelaguilogonzalez/Desktop/Màster/Python/ADIVINA EL NÚMERO/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C23BDB-1A74-B548-8902-648F9755445C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="620" windowWidth="28040" windowHeight="16220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="160" yWindow="620" windowWidth="28040" windowHeight="16220" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Solitario" sheetId="1" r:id="rId1"/>
-    <sheet name="Pareja" sheetId="2" r:id="rId2"/>
-    <sheet name="Resultado jugadores" sheetId="3" r:id="rId3"/>
+    <sheet name="Solitario" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Pareja" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Resultado jugadores" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
-  <si>
-    <t>Nombre</t>
-  </si>
-  <si>
-    <t>Dificultad</t>
-  </si>
-  <si>
-    <t>Final</t>
-  </si>
-  <si>
-    <t>Nº de intentos</t>
-  </si>
-  <si>
-    <t>Numero secreto</t>
-  </si>
-  <si>
-    <t>Último intento</t>
-  </si>
-  <si>
-    <t>Miki</t>
-  </si>
-  <si>
-    <t>Difícil</t>
-  </si>
-  <si>
-    <t>Derrota</t>
-  </si>
-  <si>
-    <t>Jugador 1</t>
-  </si>
-  <si>
-    <t>Jugador 2</t>
-  </si>
-  <si>
-    <t>Ganador</t>
-  </si>
-  <si>
-    <t>Nº de intentos Jugador 1</t>
-  </si>
-  <si>
-    <t>Nº de intentos jugador 2</t>
-  </si>
-  <si>
-    <t>Resultados partidas modo difícil</t>
-  </si>
-  <si>
-    <t>Resultados partidas modo intermedio</t>
-  </si>
-  <si>
-    <t>Resultados partidas modo fácil</t>
-  </si>
-  <si>
-    <t>Partidas en solitario</t>
-  </si>
-  <si>
-    <t>Partidas en pareja</t>
-  </si>
-  <si>
-    <t>Resultados partidas en pareja</t>
-  </si>
-  <si>
-    <t>Resultados partidas solitario</t>
-  </si>
-  <si>
-    <t>Porcentaje de victorias solitario</t>
-  </si>
-  <si>
-    <t>Porcentaje de victorias pareja</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Aptos Narrow"/>
+      <b val="1"/>
+      <color theme="0"/>
       <sz val="12"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -155,23 +76,82 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -491,52 +471,126 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="4" max="4" width="13.33203125" customWidth="1"/>
-    <col min="5" max="5" width="14.1640625" customWidth="1"/>
+    <col width="13.33203125" customWidth="1" min="4" max="4"/>
+    <col width="14.1640625" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Nombre</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Dificultad</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Nº de intentos</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Numero secreto</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Último intento</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Miki</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Difícil</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Derrota</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2" t="n">
+        <v>123</v>
+      </c>
+      <c r="F2" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Miki</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Difícil</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Derrota</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>5</v>
       </c>
+      <c r="E3" t="n">
+        <v>373</v>
+      </c>
+      <c r="F3" t="n">
+        <v>400</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2">
-        <v>6</v>
-      </c>
-      <c r="E2">
-        <v>123</v>
-      </c>
-      <c r="F2">
-        <v>75</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Miquel Àngel</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Fácil</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>17</v>
+      </c>
+      <c r="E4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F4" t="n">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -545,33 +599,49 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="4" max="4" width="21.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
+    <col width="21.5" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="21.1640625" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Jugador 1</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Jugador 2</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Ganador</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Nº de intentos Jugador 1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Nº de intentos jugador 2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Último intento</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -580,49 +650,73 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="2" max="2" width="28.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.1640625" bestFit="1" customWidth="1"/>
+    <col width="28.33203125" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="32.6640625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="27.33203125" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="17.83203125" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="16" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="25.83203125" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="25.1640625" bestFit="1" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>22</v>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Nombre</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Resultados partidas modo difícil</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Resultados partidas modo intermedio</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Resultados partidas modo fácil</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Partidas en solitario</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Partidas en pareja</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Resultados partidas en pareja</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Resultados partidas solitario</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Porcentaje de victorias solitario</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Porcentaje de victorias pareja</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Resultados de adivina el número.xlsx
+++ b/Resultados de adivina el número.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="13.33203125" customWidth="1" min="4" max="4"/>
@@ -591,6 +591,32 @@
       </c>
       <c r="F4" t="n">
         <v>21</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Miki</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Difícil</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Derrota</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>208</v>
+      </c>
+      <c r="F5" t="n">
+        <v>223</v>
       </c>
     </row>
   </sheetData>
@@ -604,12 +630,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="21.5" bestFit="1" customWidth="1" min="4" max="4"/>
     <col width="21.1640625" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="21.1640625" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -625,7 +652,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Ganador</t>
+          <t>Ganador/a</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -640,7 +667,43 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Número Secreto</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Último intento</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Miki</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>671</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>671-666</t>
         </is>
       </c>
     </row>

--- a/Resultados de adivina el número.xlsx
+++ b/Resultados de adivina el número.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="160" yWindow="620" windowWidth="28040" windowHeight="16220" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="160" yWindow="620" windowWidth="28040" windowHeight="16220" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Solitario" sheetId="1" state="visible" r:id="rId1"/>
@@ -75,10 +75,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -476,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="13.33203125" customWidth="1" min="4" max="4"/>
@@ -532,91 +534,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>123</v>
+        <v>853</v>
       </c>
       <c r="F2" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Miki</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Difícil</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Derrota</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E3" t="n">
-        <v>373</v>
-      </c>
-      <c r="F3" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Miquel Àngel</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Fácil</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Victoria</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>17</v>
-      </c>
-      <c r="E4" t="n">
-        <v>21</v>
-      </c>
-      <c r="F4" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Miki</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Difícil</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Derrota</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E5" t="n">
-        <v>208</v>
-      </c>
-      <c r="F5" t="n">
-        <v>223</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -630,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="21.5" bestFit="1" customWidth="1" min="4" max="4"/>
@@ -679,31 +603,186 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>Miki</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>Laia</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Laia</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>448</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>453-448</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>Miki</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Carlos</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Laia</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>201</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>9-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Miki</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Laia</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>990</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>432-125</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Laia</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Miki</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>410</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>765-4567</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Miki</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Laia</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Miki</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>4</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E6" t="n">
         <v>4</v>
       </c>
-      <c r="F2" t="n">
-        <v>671</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>671-666</t>
+      <c r="F6" t="n">
+        <v>507</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>507-510</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Miki</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Laia</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>744</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>624-627</t>
         </is>
       </c>
     </row>
@@ -718,7 +797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="28.33203125" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -726,7 +805,7 @@
     <col width="27.33203125" bestFit="1" customWidth="1" min="4" max="4"/>
     <col width="17.83203125" bestFit="1" customWidth="1" min="5" max="5"/>
     <col width="16" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="25.83203125" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="28.6640625" customWidth="1" min="7" max="7"/>
     <col width="25.1640625" bestFit="1" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -763,23 +842,91 @@
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>Resultados partidas en pareja</t>
+          <t>Victorias solitario</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>Resultados partidas solitario</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
+          <t>Victorias en pareja</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>Porcentaje de victorias solitario</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Porcentaje de victorias pareja</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Miki</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Laia</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
